--- a/crl_results.xlsx
+++ b/crl_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,30 +458,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
@@ -500,28 +505,31 @@
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>31.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>38.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -540,28 +548,31 @@
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>88.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>300.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -580,28 +591,31 @@
       <c r="D4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>79.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>11.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -620,28 +634,31 @@
       <c r="D5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>15.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>13.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -660,28 +677,31 @@
       <c r="D6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>63.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>61.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -700,28 +720,31 @@
       <c r="D7" t="n">
         <v>0.3</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>1.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>1.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -733,31 +756,32 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>46.17 ± 32.54</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
           <t>70.67 ± 104.48</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.83</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="K8" s="1" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -793,45 +817,50 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -850,41 +879,44 @@
       <c r="D12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>91.87 ± 108.10</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.83</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>92.14 ± 113.71</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>193.00 ± 102.70</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.65</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>22.99 ± 29.56</t>
         </is>
@@ -903,41 +935,44 @@
       <c r="D13" t="n">
         <v>0.3</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>72.85 ± 100.70</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.89</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>96.14 ± 116.93</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.79</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>172.23 ± 116.95</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.64</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>23.04 ± 33.56</t>
         </is>
@@ -956,41 +991,44 @@
       <c r="D14" t="n">
         <v>0.3</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>84.13 ± 107.33</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.83</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>85.41 ± 108.82</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0.83</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>210.47 ± 104.43</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.53</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>22.70 ± 29.78</t>
         </is>
@@ -1009,41 +1047,44 @@
       <c r="D15" t="n">
         <v>0.3</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>96.03 ± 109.34</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.83</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>98.25 ± 117.95</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.77</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>201.45 ± 109.44</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.54</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>21.20 ± 28.27</t>
         </is>
@@ -1062,41 +1103,44 @@
       <c r="D16" t="n">
         <v>0.3</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>83.01 ± 93.59</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.9</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>98.56 ± 103.89</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.87</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>218.66 ± 102.58</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.46</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>12.99 ± 20.61</t>
         </is>
@@ -1115,41 +1159,44 @@
       <c r="D17" t="n">
         <v>0.3</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>98.85 ± 108.25</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.83</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>102.91 ± 112.80</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>233.70 ± 100.37</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>0.38</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>15.36 ± 18.84</t>
         </is>
@@ -1161,44 +1208,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr"/>
-      <c r="D18" s="1" t="inlineStr"/>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>87.79 ± 105.07</t>
         </is>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="G18" s="1" t="n">
         <v>0.85</v>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
           <t>95.57 ± 112.59</t>
         </is>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="J18" s="1" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
           <t>204.92 ± 107.99</t>
         </is>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>0.53</v>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="N18" s="1" t="inlineStr">
         <is>
           <t>19.71 ± 27.58</t>
         </is>
@@ -1215,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1241,45 +1289,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -1298,41 +1351,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>137.73 ± 132.93</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.64</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>124.95 ± 129.61</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.7</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>203.78 ± 108.38</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.55</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>40.19 ± 38.08</t>
         </is>
@@ -1351,41 +1407,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>131.65 ± 134.78</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.65</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.37 ± 3.58</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>130.51 ± 131.18</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.66</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>195.97 ± 111.14</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.58</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>43.71 ± 45.88</t>
         </is>
@@ -1404,41 +1463,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>140.98 ± 129.74</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.64</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>117.34 ± 119.84</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.76</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>207.34 ± 107.56</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>44.94 ± 41.53</t>
         </is>
@@ -1457,41 +1519,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>120.93 ± 126.92</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.71</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>101.41 ± 116.95</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.8</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>194.52 ± 107.48</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.59</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>35.93 ± 39.41</t>
         </is>
@@ -1510,41 +1575,44 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>105.02 ± 112.91</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.77</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>108.03 ± 112.95</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>230.93 ± 100.51</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.42</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>34.09 ± 32.04</t>
         </is>
@@ -1563,41 +1631,44 @@
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>128.06 ± 123.60</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.73</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>114.46 ± 114.48</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.78</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>242.52 ± 85.20</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.39</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>39.38 ± 32.85</t>
         </is>
@@ -1609,46 +1680,512 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>127.39 ± 127.58</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>0.06 ± 1.47</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>116.12 ± 121.43</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
           <t>212.51 ± 105.29</t>
         </is>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.52</v>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>39.71 ± 38.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.3, dc=0.1) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>14.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>8.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>197.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>181.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>27.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>31.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>55.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>73.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>115.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>15.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>33.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>300</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>142.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>66.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>69.67 ± 105.56</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>111.50 ± 107.26</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>213.00 ± 94.64</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>22.83 ± 22.80</t>
         </is>
       </c>
     </row>
@@ -1663,7 +2200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1689,45 +2226,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -1750,41 +2292,44 @@
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>568.49 ± 438.30</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.55</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>765.24 ± 409.79</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.25</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>750.69 ± 359.82</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.37</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>57.35 ± 51.38</t>
         </is>
@@ -1796,44 +2341,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>568.49 ± 438.30</t>
         </is>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.55</v>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
           <t>765.24 ± 409.79</t>
         </is>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
           <t>750.69 ± 359.82</t>
         </is>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.37</v>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>57.35 ± 51.38</t>
         </is>
@@ -1869,45 +2415,50 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -1930,41 +2481,44 @@
       <c r="D7" t="n">
         <v>0.7</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>516.72 ± 425.22</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.01 ± 0.10</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>732.53 ± 429.17</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.29</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>761.88 ± 348.80</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.36</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>55.10 ± 53.83</t>
         </is>
@@ -1976,44 +2530,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>516.72 ± 425.22</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.61</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>0.01 ± 0.10</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>732.53 ± 429.17</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
           <t>761.88 ± 348.80</t>
         </is>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.36</v>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>55.10 ± 53.83</t>
         </is>
@@ -2030,7 +2585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2056,45 +2611,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -2115,41 +2675,44 @@
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>267.77 ± 308.79</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.78</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.02 ± 0.13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>297.12 ± 330.14</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.73</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.07 ± 0.51</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>537.77 ± 312.69</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.47</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>49.28 ± 56.75</t>
         </is>
@@ -2170,41 +2733,44 @@
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>191.98 ± 247.87</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.88</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>226.98 ± 281.63</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.85</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>607.78 ± 277.59</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.4</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>51.35 ± 47.77</t>
         </is>
@@ -2225,41 +2791,44 @@
       <c r="D4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>244.40 ± 260.59</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>297.58 ± 312.56</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.75</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>638.28 ± 269.91</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.28</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>51.05 ± 51.60</t>
         </is>
@@ -2280,41 +2849,44 @@
       <c r="D5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>326.52 ± 311.93</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.77</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>380.83 ± 311.95</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.72</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>673.75 ± 252.76</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.22</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>46.62 ± 42.01</t>
         </is>
@@ -2335,41 +2907,44 @@
       <c r="D6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>323.65 ± 287.10</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.83</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>327.42 ± 305.96</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.78</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>704.43 ± 193.50</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.23</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>40.50 ± 38.31</t>
         </is>
@@ -2381,44 +2956,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>270.86 ± 288.87</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.82</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>0.00 ± 0.06</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>305.99 ± 312.85</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.77</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>0.01 ± 0.23</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>632.40 ± 270.37</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>47.76 ± 47.91</t>
         </is>
@@ -2435,7 +3011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2461,45 +3037,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -2520,41 +3101,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>254.71 ± 339.84</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.74</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>514.88 ± 369.35</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.39</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>39.81 ± 143.25</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>510.40 ± 318.25</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>54.59 ± 62.41</t>
         </is>
@@ -2575,41 +3159,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>172.23 ± 281.45</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.84</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>484.55 ± 379.88</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.41</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>37.83 ± 103.57</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>559.69 ± 290.47</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.46</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>55.58 ± 50.96</t>
         </is>
@@ -2630,41 +3217,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>145.76 ± 244.36</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.89</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.01 ± 0.10</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>533.54 ± 366.02</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.36</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>29.83 ± 73.30</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>604.98 ± 278.04</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.41</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>51.47 ± 48.15</t>
         </is>
@@ -2685,41 +3275,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>166.14 ± 232.22</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.91</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>599.85 ± 338.40</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.26</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>22.38 ± 61.81</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>644.65 ± 255.25</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.35</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>44.97 ± 38.53</t>
         </is>
@@ -2740,41 +3333,44 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>200.36 ± 231.71</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.95</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>484.63 ± 379.69</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.42</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>7.54 ± 29.13</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>654.63 ± 245.80</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.33</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>30.38 ± 31.57</t>
         </is>
@@ -2786,44 +3382,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>187.84 ± 271.71</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.87</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>0.00 ± 0.04</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>523.49 ± 369.44</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.37</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>27.48 ± 91.63</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>594.87 ± 283.92</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.41</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>47.40 ± 48.42</t>
         </is>
@@ -2840,7 +3437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2866,45 +3463,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -2923,41 +3525,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>310.66 ± 186.06</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.64</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>442.20 ± 155.67</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.13</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>422.82 ± 148.08</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>68.31 ± 55.60</t>
         </is>
@@ -2976,41 +3581,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>341.07 ± 206.66</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.44</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>430.98 ± 171.07</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.14</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>422.53 ± 155.08</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.27</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>69.14 ± 58.10</t>
         </is>
@@ -3029,41 +3637,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>255.53 ± 204.01</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.68</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>355.29 ± 221.51</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
+      <c r="J4" t="n">
+        <v>0.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>392.03 ± 161.15</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.38</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>41.75 ± 36.24</t>
         </is>
@@ -3082,41 +3693,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>343.56 ± 184.94</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.51</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>452.42 ± 143.37</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>401.89 ± 161.23</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.32</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>48.79 ± 43.25</t>
         </is>
@@ -3135,41 +3749,44 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>292.64 ± 199.59</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.57</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>434.98 ± 162.73</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.14</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>426.63 ± 145.84</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.24</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>32.92 ± 31.25</t>
         </is>
@@ -3188,41 +3805,44 @@
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>317.26 ± 207.67</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.49</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>402.45 ± 195.19</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.2</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>457.25 ± 117.38</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.15</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>36.66 ± 35.35</t>
         </is>
@@ -3234,44 +3854,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>310.12 ± 200.63</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
           <t>419.72 ± 179.85</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.17</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
           <t>420.52 ± 150.30</t>
         </is>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.27</v>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>49.59 ± 46.76</t>
         </is>
@@ -3288,7 +3909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3314,45 +3935,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -3373,41 +3999,44 @@
       <c r="D2" t="n">
         <v>0.7</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>367.25 ± 488.49</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>340.68 ± 464.56</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.8</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>608.48 ± 429.28</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.75</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>98.87 ± 101.28</t>
         </is>
@@ -3428,41 +4057,44 @@
       <c r="D3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>400.59 ± 472.38</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>334.69 ± 428.43</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.83</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>711.41 ± 453.42</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.63</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>90.17 ± 89.26</t>
         </is>
@@ -3483,41 +4115,44 @@
       <c r="D4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>369.23 ± 439.95</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.84</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>276.98 ± 399.51</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.87</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>808.14 ± 444.57</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.55</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>71.65 ± 62.49</t>
         </is>
@@ -3538,41 +4173,44 @@
       <c r="D5" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>477.03 ± 463.90</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.79</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>357.29 ± 397.42</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.89</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>850.10 ± 425.61</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.49</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>64.90 ± 51.20</t>
         </is>
@@ -3593,41 +4231,44 @@
       <c r="D6" t="n">
         <v>0.7</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>441.10 ± 447.89</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>326.08 ± 374.76</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.89</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>826.18 ± 432.50</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.51</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>47.00 ± 42.82</t>
         </is>
@@ -3639,44 +4280,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>411.04 ± 464.79</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
           <t>327.14 ± 414.98</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.86</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
           <t>760.86 ± 446.28</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.59</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>74.52 ± 75.21</t>
         </is>
@@ -3693,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3719,45 +4361,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -3776,41 +4423,44 @@
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>503.78 ± 439.48</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.63</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>22.84 ± 83.24</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>549.44 ± 453.75</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>30.62 ± 96.96</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>703.74 ± 403.80</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.4</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>47.22 ± 96.61</t>
         </is>
@@ -3829,41 +4479,44 @@
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>400.31 ± 425.68</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.71</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>23.02 ± 109.11</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>468.04 ± 450.95</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.65</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>43.60 ± 168.32</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>587.96 ± 423.56</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.53</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>21.64 ± 56.23</t>
         </is>
@@ -3882,41 +4535,44 @@
       <c r="D4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>647.24 ± 437.83</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.41</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>23.09 ± 65.92</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>640.50 ± 430.97</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.44</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>28.76 ± 111.73</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>774.93 ± 360.36</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.34</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>43.42 ± 79.26</t>
         </is>
@@ -3935,41 +4591,44 @@
       <c r="D5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>645.75 ± 430.60</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.43</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>32.50 ± 124.96</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>619.73 ± 443.89</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.44</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>18.93 ± 77.13</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>730.99 ± 379.79</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.39</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>22.91 ± 45.43</t>
         </is>
@@ -3981,44 +4640,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>549.27 ± 445.71</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.55</v>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>25.36 ± 98.57</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>569.43 ± 450.08</t>
         </is>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.52</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>30.48 ± 118.82</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>699.40 ± 398.65</t>
         </is>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.42</v>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>33.80 ± 73.11</t>
         </is>
@@ -4054,45 +4714,50 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="K9" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K9" s="1" t="inlineStr">
+      <c r="L9" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="M9" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
+      <c r="N9" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -4111,41 +4776,44 @@
       <c r="D10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>504.18 ± 463.11</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.58</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>26.92 ± 120.33</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>522.33 ± 449.50</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0.58</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>16.48 ± 60.65</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>617.13 ± 406.13</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>35.37 ± 84.60</t>
         </is>
@@ -4164,41 +4832,44 @@
       <c r="D11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>527.23 ± 451.21</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.59</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>24.50 ± 114.79</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>494.87 ± 438.04</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0.62</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>39.73 ± 167.41</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>631.08 ± 399.22</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.55</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>27.03 ± 75.41</t>
         </is>
@@ -4217,41 +4888,44 @@
       <c r="D12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>680.32 ± 423.64</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.39</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>24.85 ± 74.47</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>682.44 ± 433.78</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.39</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>20.46 ± 60.00</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>799.75 ± 356.18</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.29</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>45.54 ± 86.57</t>
         </is>
@@ -4270,41 +4944,44 @@
       <c r="D13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>670.24 ± 436.70</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.41</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>42.67 ± 159.66</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>655.09 ± 446.40</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.4</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>25.83 ± 116.81</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>762.38 ± 376.52</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.33</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>34.55 ± 72.61</t>
         </is>
@@ -4316,44 +4993,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr"/>
-      <c r="D14" s="1" t="inlineStr"/>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>595.49 ± 451.11</t>
         </is>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>29.73 ± 121.37</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>588.68 ± 449.38</t>
         </is>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="J14" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>25.62 ± 110.97</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>702.59 ± 393.19</t>
         </is>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="M14" s="1" t="n">
         <v>0.43</v>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>35.62 ± 80.29</t>
         </is>
@@ -4370,7 +5048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4396,45 +5074,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -4455,41 +5138,44 @@
       <c r="D2" t="n">
         <v>0.7</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>60.61 ± 65.04</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.97</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>60.23 ± 66.91</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.96</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>203.53 ± 107.06</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.57</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6.79 ± 11.14</t>
         </is>
@@ -4510,41 +5196,44 @@
       <c r="D3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>61.60 ± 80.70</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.93</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>75.60 ± 88.58</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.92</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>229.20 ± 103.20</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.44</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>10.20 ± 13.81</t>
         </is>
@@ -4565,41 +5254,44 @@
       <c r="D4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>84.06 ± 90.22</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>72.31 ± 84.87</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.91</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>216.38 ± 108.57</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.46</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>14.14 ± 20.68</t>
         </is>
@@ -4620,41 +5312,44 @@
       <c r="D5" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>86.29 ± 92.48</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.92</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>82.70 ± 89.02</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.91</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>206.66 ± 111.57</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.48</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>10.69 ± 15.58</t>
         </is>
@@ -4675,41 +5370,44 @@
       <c r="D6" t="n">
         <v>0.7</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>87.23 ± 98.19</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.9</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.04 ± 0.40</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>90.40 ± 101.70</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.87</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>204.41 ± 116.21</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.5</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>12.44 ± 18.25</t>
         </is>
@@ -4721,44 +5419,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>75.96 ± 86.97</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.93</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>0.01 ± 0.18</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>76.25 ± 87.53</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.91</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
           <t>212.04 ± 109.84</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>10.85 ± 16.43</t>
         </is>
@@ -4775,7 +5474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4801,45 +5500,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -4860,41 +5564,44 @@
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>176.22 ± 240.37</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.92</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>179.38 ± 241.34</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.9</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>573.25 ± 288.04</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.45</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>31.58 ± 40.33</t>
         </is>
@@ -4915,41 +5622,44 @@
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>151.65 ± 173.17</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.97</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>241.32 ± 268.84</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.87</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>573.75 ± 285.36</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.5</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>28.53 ± 30.61</t>
         </is>
@@ -4970,41 +5680,44 @@
       <c r="D4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>192.75 ± 246.45</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>302.50 ± 304.21</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.78</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>621.73 ± 276.33</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.37</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>26.42 ± 32.06</t>
         </is>
@@ -5025,41 +5738,44 @@
       <c r="D5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>244.53 ± 257.44</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.87</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>307.00 ± 289.44</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.8</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>676.93 ± 236.69</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.27</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>24.70 ± 39.71</t>
         </is>
@@ -5080,41 +5796,44 @@
       <c r="D6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>306.47 ± 292.17</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.85</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>368.72 ± 310.93</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.73</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>660.88 ± 245.83</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>19.43 ± 23.87</t>
         </is>
@@ -5126,44 +5845,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>214.32 ± 251.15</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
           <t>279.78 ± 291.29</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.82</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
           <t>621.31 ± 270.72</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.38</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>26.13 ± 34.12</t>
         </is>
@@ -5180,7 +5900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5206,45 +5926,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -5267,41 +5992,44 @@
       <c r="D2" t="n">
         <v>0.7</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>375.07 ± 395.18</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.79</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>394.14 ± 402.82</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.75</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>755.90 ± 373.10</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.32</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>29.95 ± 34.78</t>
         </is>
@@ -5313,44 +6041,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>375.07 ± 395.18</t>
         </is>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.79</v>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
           <t>394.14 ± 402.82</t>
         </is>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
           <t>755.90 ± 373.10</t>
         </is>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>29.95 ± 34.78</t>
         </is>
@@ -5367,7 +6096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5393,45 +6122,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -5450,41 +6184,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>176.40 ± 171.75</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.87</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>183.19 ± 173.78</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>388.30 ± 183.59</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.31</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>24.62 ± 28.73</t>
         </is>
@@ -5503,41 +6240,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>240.43 ± 198.35</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.73</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>220.11 ± 203.73</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.74</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>409.48 ± 163.49</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>42.43 ± 50.91</t>
         </is>
@@ -5556,41 +6296,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>189.45 ± 187.75</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.8</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>216.09 ± 199.38</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.74</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>404.36 ± 166.33</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.29</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>25.60 ± 28.57</t>
         </is>
@@ -5609,41 +6352,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>234.59 ± 183.36</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.78</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>193.40 ± 177.28</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.84</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>421.86 ± 144.21</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.28</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>24.05 ± 29.24</t>
         </is>
@@ -5662,41 +6408,44 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>253.62 ± 189.57</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.71</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>242.99 ± 203.81</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.72</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>420.88 ± 145.43</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.27</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>16.14 ± 23.54</t>
         </is>
@@ -5715,41 +6464,44 @@
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>249.04 ± 203.51</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>263.51 ± 199.90</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.67</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>458.51 ± 109.93</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.15</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>20.29 ± 26.37</t>
         </is>
@@ -5761,44 +6513,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>223.92 ± 191.66</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.76</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
           <t>219.88 ± 195.31</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.76</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
           <t>417.23 ± 155.42</t>
         </is>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.27</v>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>25.52 ± 33.52</t>
         </is>
@@ -5815,7 +6568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5841,45 +6594,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -5900,41 +6658,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>160.86 ± 274.89</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.85</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>486.59 ± 384.17</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.4</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>502.93 ± 322.52</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>23.35 ± 30.46</t>
         </is>
@@ -5955,41 +6716,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>137.23 ± 218.49</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>461.28 ± 390.01</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.43</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>548.67 ± 288.28</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.51</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>29.90 ± 34.42</t>
         </is>
@@ -6010,41 +6774,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>129.94 ± 234.24</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>479.02 ± 385.22</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.41</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>548.48 ± 298.02</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.52</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>26.07 ± 32.64</t>
         </is>
@@ -6065,41 +6832,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>166.01 ± 229.60</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.93</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.09 ± 0.90</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>423.08 ± 388.80</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.49</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>612.73 ± 275.40</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.38</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>24.45 ± 30.44</t>
         </is>
@@ -6120,41 +6890,44 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>179.70 ± 248.87</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.9</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>484.40 ± 379.31</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.41</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>618.16 ± 283.98</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.38</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>18.35 ± 26.54</t>
         </is>
@@ -6166,44 +6939,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>154.75 ± 242.71</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.91</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>0.02 ± 0.40</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>466.87 ± 386.24</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.43</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
           <t>566.19 ± 297.29</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>24.42 ± 31.24</t>
         </is>
@@ -6220,7 +6994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,45 +7020,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -6305,41 +7084,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>255.42 ± 387.54</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.88</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>213.37 ± 337.45</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.91</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>557.42 ± 462.91</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.72</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>50.07 ± 59.25</t>
         </is>
@@ -6360,41 +7142,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>255.10 ± 336.57</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.93</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>313.58 ± 410.18</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.86</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>657.63 ± 451.96</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>42.76 ± 47.03</t>
         </is>
@@ -6415,41 +7200,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>255.91 ± 312.58</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>231.59 ± 313.72</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.93</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>723.68 ± 436.27</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.62</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>31.80 ± 34.04</t>
         </is>
@@ -6470,41 +7258,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>302.57 ± 368.62</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.92</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>286.30 ± 351.12</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.93</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>829.16 ± 439.80</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.51</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>28.10 ± 28.48</t>
         </is>
@@ -6525,41 +7316,44 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>362.26 ± 381.98</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.89</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>305.34 ± 363.84</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.9</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>839.12 ± 433.69</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.48</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>28.58 ± 36.61</t>
         </is>
@@ -6571,44 +7365,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>286.25 ± 361.07</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.91</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
           <t>270.04 ± 358.97</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.91</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
           <t>721.40 ± 457.56</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>36.26 ± 43.38</t>
         </is>
@@ -6625,7 +7420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6651,45 +7446,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -6708,41 +7508,44 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>535.31 ± 452.28</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>13.71 ± 60.69</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>552.04 ± 448.91</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.55</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>12.78 ± 78.51</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>674.58 ± 409.03</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.45</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>25.28 ± 61.76</t>
         </is>
@@ -6761,41 +7564,44 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>425.06 ± 425.32</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2.10 ± 11.42</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>456.48 ± 440.51</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.67</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2.67 ± 13.92</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>587.72 ± 407.22</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.58</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>19.24 ± 44.40</t>
         </is>
@@ -6814,41 +7620,44 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>685.44 ± 438.62</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.37</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>8.72 ± 46.13</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>659.71 ± 444.22</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.4</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>12.43 ± 50.48</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>779.97 ± 349.85</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.36</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>24.07 ± 46.99</t>
         </is>
@@ -6867,41 +7676,44 @@
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>680.65 ± 433.07</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.38</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>15.54 ± 92.91</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>676.82 ± 436.76</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.38</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>11.73 ± 66.74</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>759.60 ± 368.58</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.34</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>16.30 ± 41.92</t>
         </is>
@@ -6913,44 +7725,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>581.62 ± 450.73</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>10.02 ± 60.59</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>586.26 ± 451.46</t>
         </is>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>9.90 ± 57.94</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>700.47 ± 391.98</t>
         </is>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.43</v>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>21.22 ± 49.51</t>
         </is>
@@ -6967,7 +7780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6993,45 +7806,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -7052,41 +7870,44 @@
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>81.73 ± 94.93</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.89</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>93.89 ± 93.42</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.91</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>221.49 ± 104.14</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.48</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21.96 ± 25.91</t>
         </is>
@@ -7107,41 +7928,44 @@
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>92.53 ± 96.66</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.88</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>90.95 ± 98.86</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.87</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>216.64 ± 104.87</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.53</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>21.27 ± 25.53</t>
         </is>
@@ -7162,41 +7986,44 @@
       <c r="D4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>99.66 ± 97.33</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>84.10 ± 97.37</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.87</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>199.26 ± 113.06</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.53</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>17.52 ± 26.54</t>
         </is>
@@ -7217,41 +8044,44 @@
       <c r="D5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>92.71 ± 92.13</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.89</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>99.99 ± 99.08</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.88</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>196.66 ± 111.63</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.55</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>22.04 ± 24.48</t>
         </is>
@@ -7272,41 +8102,44 @@
       <c r="D6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>88.82 ± 104.64</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.83</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>104.23 ± 102.38</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.85</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>201.59 ± 109.16</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.54</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>15.27 ± 22.58</t>
         </is>
@@ -7318,44 +8151,45 @@
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>91.09 ± 97.41</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.87</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
           <t>94.63 ± 98.52</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.88</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
           <t>207.13 ± 109.09</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.53</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>19.61 ± 25.20</t>
         </is>

--- a/crl_results.xlsx
+++ b/crl_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta Goal</t>
+          <t>Delta G</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -489,6 +489,21 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
         </is>
       </c>
     </row>
@@ -510,11 +525,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.00 ± 0.00</t>
+          <t>91.87 ± 108.10</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -523,15 +538,28 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>38.00 ± 0.00</t>
+          <t>92.14 ± 113.71</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>193.00 ± 102.70</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>22.99 ± 29.56</t>
         </is>
       </c>
     </row>
@@ -553,11 +581,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>88.00 ± 0.00</t>
+          <t>72.85 ± 100.70</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -566,15 +594,28 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>300.00 ± 0.00</t>
+          <t>96.14 ± 116.93</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>172.23 ± 116.95</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>23.04 ± 33.56</t>
         </is>
       </c>
     </row>
@@ -596,11 +637,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79.00 ± 0.00</t>
+          <t>84.13 ± 107.33</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,15 +650,28 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11.00 ± 0.00</t>
+          <t>85.41 ± 108.82</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>210.47 ± 104.43</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>22.70 ± 29.78</t>
         </is>
       </c>
     </row>
@@ -639,11 +693,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15.00 ± 0.00</t>
+          <t>96.03 ± 109.34</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -652,15 +706,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13.00 ± 0.00</t>
+          <t>98.25 ± 117.95</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>201.45 ± 109.44</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>21.20 ± 28.27</t>
         </is>
       </c>
     </row>
@@ -682,11 +749,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63.00 ± 0.00</t>
+          <t>83.01 ± 93.59</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -695,15 +762,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.00 ± 0.00</t>
+          <t>98.56 ± 103.89</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>218.66 ± 102.58</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>12.99 ± 20.61</t>
         </is>
       </c>
     </row>
@@ -725,11 +805,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.00 ± 0.00</t>
+          <t>98.85 ± 108.25</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -738,15 +818,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.00 ± 0.00</t>
+          <t>102.91 ± 112.80</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>233.70 ± 100.37</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>15.36 ± 18.84</t>
         </is>
       </c>
     </row>
@@ -762,11 +855,11 @@
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>46.17 ± 32.54</t>
+          <t>87.79 ± 105.07</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
@@ -775,478 +868,26 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>70.67 ± 104.48</t>
+          <t>95.57 ± 112.59</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>--- NEW RUN: C-LAMAML (dt=0.3, dc=0.1) vs CRL vs Random ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Room Size</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Num Distractor</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Max Steps</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Delta G</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Delta C</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps C-LAMAML</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob C-LAMAML</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols C-LAMAML</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps CRL</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob CRL</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols CRL</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Random</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Random</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Random</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>300</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>91.87 ± 108.10</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>92.14 ± 113.71</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>193.00 ± 102.70</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>22.99 ± 29.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>72.85 ± 100.70</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>96.14 ± 116.93</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>172.23 ± 116.95</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>23.04 ± 33.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>300</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>84.13 ± 107.33</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>85.41 ± 108.82</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>210.47 ± 104.43</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>204.92 ± 107.99</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>0.53</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>22.70 ± 29.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>300</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>96.03 ± 109.34</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>98.25 ± 117.95</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>201.45 ± 109.44</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>21.20 ± 28.27</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>300</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>83.01 ± 93.59</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>98.56 ± 103.89</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>218.66 ± 102.58</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>12.99 ± 20.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>300</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>98.85 ± 108.25</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>102.91 ± 112.80</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>233.70 ± 100.37</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>15.36 ± 18.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>87.79 ± 105.07</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>95.57 ± 112.59</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t>204.92 ± 107.99</t>
-        </is>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>19.71 ± 27.58</t>
         </is>
@@ -1263,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,18 +990,18 @@
         <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>137.73 ± 132.93</t>
+          <t>14.00 ± 0.00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1369,11 +1010,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>124.95 ± 129.61</t>
+          <t>25.00 ± 0.00</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1382,15 +1023,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>203.78 ± 108.38</t>
+          <t>300.00 ± 0.00</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>40.19 ± 38.08</t>
+          <t>8.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1405,31 +1046,31 @@
         <v>300</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>131.65 ± 134.78</t>
+          <t>300.00 ± 0.00</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.37 ± 3.58</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>130.51 ± 131.18</t>
+          <t>197.00 ± 0.00</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1438,15 +1079,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>195.97 ± 111.14</t>
+          <t>181.00 ± 0.00</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>43.71 ± 45.88</t>
+          <t>27.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1461,18 +1102,18 @@
         <v>300</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>140.98 ± 129.74</t>
+          <t>15.00 ± 0.00</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1481,11 +1122,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>117.34 ± 119.84</t>
+          <t>31.00 ± 0.00</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1494,15 +1135,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>207.34 ± 107.56</t>
+          <t>55.00 ± 0.00</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>44.94 ± 41.53</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1517,18 +1158,18 @@
         <v>300</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>120.93 ± 126.92</t>
+          <t>73.00 ± 0.00</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1537,11 +1178,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>101.41 ± 116.95</t>
+          <t>115.00 ± 0.00</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1550,15 +1191,15 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>194.52 ± 107.48</t>
+          <t>300.00 ± 0.00</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>35.93 ± 39.41</t>
+          <t>3.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1573,18 +1214,18 @@
         <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>105.02 ± 112.91</t>
+          <t>15.00 ± 0.00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1593,11 +1234,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>108.03 ± 112.95</t>
+          <t>300.00 ± 0.00</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1606,15 +1247,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>230.93 ± 100.51</t>
+          <t>300.00 ± 0.00</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>34.09 ± 32.04</t>
+          <t>33.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1629,18 +1270,18 @@
         <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>128.06 ± 123.60</t>
+          <t>1.00 ± 0.00</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1649,11 +1290,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>114.46 ± 114.48</t>
+          <t>1.00 ± 0.00</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1662,15 +1303,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>242.52 ± 85.20</t>
+          <t>142.00 ± 0.00</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>39.38 ± 32.85</t>
+          <t>66.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1327,24 @@
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>127.39 ± 127.58</t>
+          <t>69.67 ± 105.56</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>0.06 ± 1.47</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>116.12 ± 121.43</t>
+          <t>111.50 ± 107.26</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
@@ -1712,478 +1353,13 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>212.51 ± 105.29</t>
+          <t>213.00 ± 94.64</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>39.71 ± 38.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>--- NEW RUN: C-LAMAML (dt=0.3, dc=0.1) vs CRL vs Random ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Room Size</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Num Distractor</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Max Steps</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Delta G</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Delta C</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps C-LAMAML</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob C-LAMAML</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols C-LAMAML</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps CRL</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob CRL</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols CRL</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Random</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Random</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Random</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>300</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>14.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>300.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8.00 ± 0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>300.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>197.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>181.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>27.00 ± 0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>300</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>15.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>31.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>55.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>300</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>73.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>115.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>300.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>3.00 ± 0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>300</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>15.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>300.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>300.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>33.00 ± 0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>300</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>142.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>66.00 ± 0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>69.67 ± 105.56</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>111.50 ± 107.26</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t>213.00 ± 94.64</t>
-        </is>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
         <is>
           <t>22.83 ± 22.80</t>
         </is>
@@ -2200,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,31 +1466,31 @@
         <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>568.49 ± 438.30</t>
+          <t>516.72 ± 425.22</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>765.24 ± 409.79</t>
+          <t>732.53 ± 429.17</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2323,15 +1499,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>750.69 ± 359.82</t>
+          <t>761.88 ± 348.80</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>57.35 ± 51.38</t>
+          <t>55.10 ± 53.83</t>
         </is>
       </c>
     </row>
@@ -2347,24 +1523,24 @@
       <c r="E3" s="1" t="n"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>568.49 ± 438.30</t>
+          <t>516.72 ± 425.22</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>765.24 ± 409.79</t>
+          <t>732.53 ± 429.17</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
@@ -2373,202 +1549,13 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>750.69 ± 359.82</t>
+          <t>761.88 ± 348.80</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>57.35 ± 51.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>--- NEW RUN: C-LAMAML (dt=0.7, dc=0.3) vs CRL vs Random ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Room Size</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Num Distractor</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Max Steps</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Delta G</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Delta C</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps C-LAMAML</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob C-LAMAML</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols C-LAMAML</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps CRL</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob CRL</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols CRL</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Random</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Random</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Random</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>516.72 ± 425.22</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.01 ± 0.10</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>732.53 ± 429.17</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>761.88 ± 348.80</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>55.10 ± 53.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>516.72 ± 425.22</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>0.01 ± 0.10</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>732.53 ± 429.17</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>761.88 ± 348.80</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>55.10 ± 53.83</t>
         </is>
@@ -4335,7 +3322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4421,48 +3408,48 @@
         <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>503.78 ± 439.48</t>
+          <t>504.18 ± 463.11</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.84 ± 83.24</t>
+          <t>26.92 ± 120.33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>549.44 ± 453.75</t>
+          <t>522.33 ± 449.50</t>
         </is>
       </c>
       <c r="J2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>16.48 ± 60.65</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>617.13 ± 406.13</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>30.62 ± 96.96</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>703.74 ± 403.80</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0.4</v>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>47.22 ± 96.61</t>
+          <t>35.37 ± 84.60</t>
         </is>
       </c>
     </row>
@@ -4477,48 +3464,48 @@
         <v>1000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>400.31 ± 425.68</t>
+          <t>527.23 ± 451.21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>23.02 ± 109.11</t>
+          <t>24.50 ± 114.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>468.04 ± 450.95</t>
+          <t>494.87 ± 438.04</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.60 ± 168.32</t>
+          <t>39.73 ± 167.41</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>587.96 ± 423.56</t>
+          <t>631.08 ± 399.22</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>21.64 ± 56.23</t>
+          <t>27.03 ± 75.41</t>
         </is>
       </c>
     </row>
@@ -4533,48 +3520,48 @@
         <v>1000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>647.24 ± 437.83</t>
+          <t>680.32 ± 423.64</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23.09 ± 65.92</t>
+          <t>24.85 ± 74.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>640.50 ± 430.97</t>
+          <t>682.44 ± 433.78</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28.76 ± 111.73</t>
+          <t>20.46 ± 60.00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>774.93 ± 360.36</t>
+          <t>799.75 ± 356.18</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>43.42 ± 79.26</t>
+          <t>45.54 ± 86.57</t>
         </is>
       </c>
     </row>
@@ -4589,48 +3576,48 @@
         <v>1000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>645.75 ± 430.60</t>
+          <t>670.24 ± 436.70</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>32.50 ± 124.96</t>
+          <t>42.67 ± 159.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>619.73 ± 443.89</t>
+          <t>655.09 ± 446.40</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18.93 ± 77.13</t>
+          <t>25.83 ± 116.81</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>730.99 ± 379.79</t>
+          <t>762.38 ± 376.52</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22.91 ± 45.43</t>
+          <t>34.55 ± 72.61</t>
         </is>
       </c>
     </row>
@@ -4646,392 +3633,39 @@
       <c r="E6" s="1" t="n"/>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>549.27 ± 445.71</t>
+          <t>595.49 ± 451.11</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>25.36 ± 98.57</t>
+          <t>29.73 ± 121.37</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>569.43 ± 450.08</t>
+          <t>588.68 ± 449.38</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>30.48 ± 118.82</t>
+          <t>25.62 ± 110.97</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>699.40 ± 398.65</t>
+          <t>702.59 ± 393.19</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>33.80 ± 73.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Room Size</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Num Distractor</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Max Steps</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Delta G</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Delta C</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps C-LAMAML</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob C-LAMAML</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols C-LAMAML</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps CRL</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob CRL</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols CRL</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Random</t>
-        </is>
-      </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Random</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Random</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>504.18 ± 463.11</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>26.92 ± 120.33</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>522.33 ± 449.50</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>16.48 ± 60.65</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>617.13 ± 406.13</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>35.37 ± 84.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>527.23 ± 451.21</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>24.50 ± 114.79</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>494.87 ± 438.04</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>39.73 ± 167.41</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>631.08 ± 399.22</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>27.03 ± 75.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>680.32 ± 423.64</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>24.85 ± 74.47</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>682.44 ± 433.78</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>20.46 ± 60.00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>799.75 ± 356.18</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>45.54 ± 86.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>670.24 ± 436.70</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>42.67 ± 159.66</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>655.09 ± 446.40</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>25.83 ± 116.81</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>762.38 ± 376.52</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>34.55 ± 72.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>595.49 ± 451.11</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>29.73 ± 121.37</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>588.68 ± 449.38</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>25.62 ± 110.97</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>702.59 ± 393.19</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>35.62 ± 80.29</t>
         </is>

--- a/crl_results.xlsx
+++ b/crl_results.xlsx
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1362,6 +1362,471 @@
       <c r="N8" s="1" t="inlineStr">
         <is>
           <t>22.83 ± 22.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.3, dc=0.1) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>144.72 ± 131.98</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>122.87 ± 128.30</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>208.48 ± 102.28</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>40.34 ± 39.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>133.48 ± 134.82</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>125.34 ± 133.78</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>181.16 ± 117.99</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>36.21 ± 42.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>148.17 ± 130.67</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>119.23 ± 125.06</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>197.63 ± 105.82</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>38.77 ± 39.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>117.65 ± 126.29</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>109.89 ± 120.35</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>203.37 ± 118.14</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>39.50 ± 43.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>104.84 ± 108.72</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>108.61 ± 113.23</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>245.44 ± 88.03</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>35.83 ± 34.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>300</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>141.59 ± 125.62</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>112.16 ± 119.25</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>242.46 ± 92.55</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>41.50 ± 33.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>131.74 ± 127.59</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>116.35 ± 123.68</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>213.09 ± 107.34</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>38.69 ± 38.92</t>
         </is>
       </c>
     </row>
